--- a/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/report/chb/businessdatamaintain/chbprdbaseinfo/CchbPrdBaseInfo001.xlsx
+++ b/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/report/chb/businessdatamaintain/chbprdbaseinfo/CchbPrdBaseInfo001.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>产品代码</t>
   </si>
@@ -137,39 +137,6 @@
   </si>
   <si>
     <t>错误信息</t>
-  </si>
-  <si>
-    <t>01 集合管理</t>
-  </si>
-  <si>
-    <t>01 是</t>
-  </si>
-  <si>
-    <t>01 有规律开放</t>
-  </si>
-  <si>
-    <t>01 每天开放</t>
-  </si>
-  <si>
-    <t>01申赎皆可</t>
-  </si>
-  <si>
-    <t>N 净值</t>
-  </si>
-  <si>
-    <t>01 发行成功</t>
-  </si>
-  <si>
-    <t>A/360</t>
-  </si>
-  <si>
-    <t>01 主动管理</t>
-  </si>
-  <si>
-    <t>01 收益权转让</t>
-  </si>
-  <si>
-    <t>1-单位</t>
   </si>
 </sst>
 </file>
@@ -178,9 +145,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -204,16 +171,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -239,10 +207,18 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -254,17 +230,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,42 +253,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -325,9 +269,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -346,6 +306,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -356,187 +323,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,21 +533,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -597,8 +549,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -608,18 +562,37 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,17 +612,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,10 +635,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -680,16 +647,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -698,115 +665,115 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1286,66 +1253,36 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
-      <c r="V2" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="V2" s="2"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
-      <c r="Z2" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
-      <c r="AB2" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
-      <c r="AF2" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
-      <c r="AH2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
@@ -2276,11 +2213,11 @@
     </row>
   </sheetData>
   <dataValidations count="11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K23 V2:V23 AH2:AH23 AI2:AI23 AM2:AM23">
+      <formula1>"01 是,02 否"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J23">
       <formula1>"01 集合管理,02 单独管理"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K23 V2:V23 AH2:AH23 AI2:AI23 AM2:AM23">
-      <formula1>"01 是,02 否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z23">
       <formula1>"N 净值,M 货币,R 利率"</formula1>
@@ -2291,14 +2228,14 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB23">
       <formula1>"01 发行成功,02 发行失败,03 确认发行"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q23">
-      <formula1>"01 每天开放,02 每周开放一次,03 每两周开放一次,04每月开放一次,05每季度开放一次,06 每半年开放一次,07 每年开放一次,99 其他规律开放周期"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576">
+      <formula1>"01 每天开放,02 每周开放一次,03 每两周开放一次,04 每月开放一次,05 每季度开放一次,06 每半年开放一次,07 每年开放一次,99 其他规律开放周期"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF23">
-      <formula1>"A/360,A/365"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576">
+      <formula1>"01 申赎皆可,02 仅可申购无限制,03 仅可赎回无限制,04 仅可申购有限制,05 仅可赎回有限制,99 其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X23">
-      <formula1>"01申赎皆可,02仅可申购无限制,03仅可赎回无限制,04仅可申购有限制,05仅可赎回有限制,99其他"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576">
+      <formula1>"A/360 A/360,A/365 A/365"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ23">
       <formula1>"01 主动管理,02 被动管理"</formula1>
@@ -2306,8 +2243,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2:AK23">
       <formula1>"01 收益权转让,99 其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2:AL23">
-      <formula1>"1-单位,2-个人,3-个人及单位"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2:AL1048576">
+      <formula1>"1 单位,2 个人,3 个人及单位"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/report/chb/businessdatamaintain/chbprdbaseinfo/CchbPrdBaseInfo001.xlsx
+++ b/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/report/chb/businessdatamaintain/chbprdbaseinfo/CchbPrdBaseInfo001.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\feature3.0.6\tams\tams-svreport-parent\tams-svreport-chb\src\main\resources\tpl\report\chb\businessdatamaintain\chbprdbaseinfo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9300"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息导入模板" sheetId="1" r:id="rId1"/>
@@ -14,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>产品代码</t>
   </si>
@@ -142,14 +147,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,345 +169,21 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -531,251 +206,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -787,61 +220,17 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1099,23 +488,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AP23"/>
-  <sheetFormatPr defaultColWidth="18.0925925925926" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AO23"/>
+  <sheetFormatPr defaultColWidth="18.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="18.0925925925926" customWidth="1"/>
-    <col min="3" max="3" width="17.0925925925926" customWidth="1"/>
-    <col min="4" max="4" width="18.0925925925926" customWidth="1"/>
-    <col min="5" max="5" width="19.2685185185185" customWidth="1"/>
-    <col min="6" max="16383" width="18.0925925925926" customWidth="1"/>
+    <col min="1" max="2" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="18.125" customWidth="1"/>
+    <col min="5" max="5" width="19.25" customWidth="1"/>
+    <col min="6" max="16382" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="43.2" spans="1:42">
+    <row r="1" spans="1:41" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1234,16 +623,13 @@
         <v>38</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP1" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:42">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1285,9 +671,8 @@
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-    </row>
-    <row r="3" spans="1:42">
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1329,9 +714,8 @@
       <c r="AM3" s="2"/>
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
-      <c r="AP3" s="2"/>
-    </row>
-    <row r="4" spans="1:42">
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1373,9 +757,8 @@
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
-      <c r="AP4" s="2"/>
-    </row>
-    <row r="5" spans="1:42">
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1417,9 +800,8 @@
       <c r="AM5" s="2"/>
       <c r="AN5" s="2"/>
       <c r="AO5" s="2"/>
-      <c r="AP5" s="2"/>
-    </row>
-    <row r="6" spans="1:42">
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1461,9 +843,8 @@
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
       <c r="AO6" s="2"/>
-      <c r="AP6" s="2"/>
-    </row>
-    <row r="7" spans="1:42">
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1505,9 +886,8 @@
       <c r="AM7" s="2"/>
       <c r="AN7" s="2"/>
       <c r="AO7" s="2"/>
-      <c r="AP7" s="2"/>
-    </row>
-    <row r="8" spans="1:42">
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1549,9 +929,8 @@
       <c r="AM8" s="2"/>
       <c r="AN8" s="2"/>
       <c r="AO8" s="2"/>
-      <c r="AP8" s="2"/>
-    </row>
-    <row r="9" spans="1:42">
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1593,9 +972,8 @@
       <c r="AM9" s="2"/>
       <c r="AN9" s="2"/>
       <c r="AO9" s="2"/>
-      <c r="AP9" s="2"/>
-    </row>
-    <row r="10" spans="1:42">
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1637,9 +1015,8 @@
       <c r="AM10" s="2"/>
       <c r="AN10" s="2"/>
       <c r="AO10" s="2"/>
-      <c r="AP10" s="2"/>
-    </row>
-    <row r="11" spans="1:42">
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1681,9 +1058,8 @@
       <c r="AM11" s="2"/>
       <c r="AN11" s="2"/>
       <c r="AO11" s="2"/>
-      <c r="AP11" s="2"/>
-    </row>
-    <row r="12" spans="1:42">
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1725,9 +1101,8 @@
       <c r="AM12" s="2"/>
       <c r="AN12" s="2"/>
       <c r="AO12" s="2"/>
-      <c r="AP12" s="2"/>
-    </row>
-    <row r="13" spans="1:42">
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1769,9 +1144,8 @@
       <c r="AM13" s="2"/>
       <c r="AN13" s="2"/>
       <c r="AO13" s="2"/>
-      <c r="AP13" s="2"/>
-    </row>
-    <row r="14" spans="1:42">
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1813,9 +1187,8 @@
       <c r="AM14" s="2"/>
       <c r="AN14" s="2"/>
       <c r="AO14" s="2"/>
-      <c r="AP14" s="2"/>
-    </row>
-    <row r="15" spans="1:42">
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1857,9 +1230,8 @@
       <c r="AM15" s="2"/>
       <c r="AN15" s="2"/>
       <c r="AO15" s="2"/>
-      <c r="AP15" s="2"/>
-    </row>
-    <row r="16" spans="1:42">
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1901,9 +1273,8 @@
       <c r="AM16" s="2"/>
       <c r="AN16" s="2"/>
       <c r="AO16" s="2"/>
-      <c r="AP16" s="2"/>
-    </row>
-    <row r="17" spans="1:42">
+    </row>
+    <row r="17" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1945,9 +1316,8 @@
       <c r="AM17" s="2"/>
       <c r="AN17" s="2"/>
       <c r="AO17" s="2"/>
-      <c r="AP17" s="2"/>
-    </row>
-    <row r="18" spans="1:42">
+    </row>
+    <row r="18" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1989,9 +1359,8 @@
       <c r="AM18" s="2"/>
       <c r="AN18" s="2"/>
       <c r="AO18" s="2"/>
-      <c r="AP18" s="2"/>
-    </row>
-    <row r="19" spans="1:42">
+    </row>
+    <row r="19" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2033,9 +1402,8 @@
       <c r="AM19" s="2"/>
       <c r="AN19" s="2"/>
       <c r="AO19" s="2"/>
-      <c r="AP19" s="2"/>
-    </row>
-    <row r="20" spans="1:42">
+    </row>
+    <row r="20" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2077,9 +1445,8 @@
       <c r="AM20" s="2"/>
       <c r="AN20" s="2"/>
       <c r="AO20" s="2"/>
-      <c r="AP20" s="2"/>
-    </row>
-    <row r="21" spans="1:42">
+    </row>
+    <row r="21" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2121,9 +1488,8 @@
       <c r="AM21" s="2"/>
       <c r="AN21" s="2"/>
       <c r="AO21" s="2"/>
-      <c r="AP21" s="2"/>
-    </row>
-    <row r="22" spans="1:42">
+    </row>
+    <row r="22" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2165,9 +1531,8 @@
       <c r="AM22" s="2"/>
       <c r="AN22" s="2"/>
       <c r="AO22" s="2"/>
-      <c r="AP22" s="2"/>
-    </row>
-    <row r="23" spans="1:42">
+    </row>
+    <row r="23" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2209,9 +1574,9 @@
       <c r="AM23" s="2"/>
       <c r="AN23" s="2"/>
       <c r="AO23" s="2"/>
-      <c r="AP23" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="11">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K23 V2:V23 AH2:AH23 AI2:AI23 AM2:AM23">
       <formula1>"01 是,02 否"</formula1>
@@ -2248,6 +1613,5 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>